--- a/app/templates/vendor_bulk_upload.xlsx
+++ b/app/templates/vendor_bulk_upload.xlsx
@@ -428,6 +428,14 @@
   </sheetPr>
   <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -534,6 +542,10 @@
   </sheetPr>
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
